--- a/17 18 20/Excel/4.Advanced Tools & Automation/Advance Formula and Functions-1.xlsx
+++ b/17 18 20/Excel/4.Advanced Tools & Automation/Advance Formula and Functions-1.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Study\Eathans\Ethans\19\1 Excel\Advance Formulas and Functions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Study\Eathans\Ethans\17 18 20\Excel\4.Advanced Tools &amp; Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
   </bookViews>
   <sheets>
     <sheet name="Vloo" sheetId="14" r:id="rId1"/>
@@ -21,15 +21,12 @@
     <sheet name="SumIF_n_CountIf" sheetId="15" r:id="rId7"/>
     <sheet name="ConditionalFunctions" sheetId="19" r:id="rId8"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId9"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">SumIF_n_CountIf!$F$1:$N$22</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId10"/>
+    <pivotCache cacheId="6" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1060" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="191">
   <si>
     <t>Male</t>
   </si>
@@ -333,9 +330,6 @@
     <t>Omkar Bhat</t>
   </si>
   <si>
-    <t>Email id</t>
-  </si>
-  <si>
     <t>emailid</t>
   </si>
   <si>
@@ -595,6 +589,32 @@
   </si>
   <si>
     <t>numchar</t>
+  </si>
+  <si>
+    <t>=SUMIFS
+(sum_range,Cri_ra1,cri1,Cri_ra2,cri2,…….)</t>
+  </si>
+  <si>
+    <t>=COUNTIFS
+(cri_range1,cri1,cri_range2,cri2)</t>
+  </si>
+  <si>
+    <t>=SUMIF
+(Range,Criteria,Sum_Range)</t>
+  </si>
+  <si>
+    <t>=COUNTIF
+(Range,criteria)</t>
+  </si>
+  <si>
+    <t>Table_01</t>
+  </si>
+  <si>
+    <t>Table_02</t>
+  </si>
+  <si>
+    <t>=VLOOKUP
+(loock_value,Table_Array,indexNumber,[True,False])</t>
   </si>
 </sst>
 </file>
@@ -605,7 +625,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -665,8 +685,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -682,6 +708,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -728,7 +760,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -833,6 +865,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -931,633 +981,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="pIVOT Table"/>
-      <sheetName val="Sheet5"/>
-      <sheetName val="Sheet4"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="A1" t="str">
-            <v>EmpID</v>
-          </cell>
-          <cell r="B1" t="str">
-            <v>Region</v>
-          </cell>
-          <cell r="C1" t="str">
-            <v>Name</v>
-          </cell>
-          <cell r="D1" t="str">
-            <v>Dept</v>
-          </cell>
-          <cell r="E1" t="str">
-            <v>Salary</v>
-          </cell>
-          <cell r="F1" t="str">
-            <v>Bonus</v>
-          </cell>
-          <cell r="G1" t="str">
-            <v>Rating</v>
-          </cell>
-          <cell r="H1" t="str">
-            <v>JoinDate</v>
-          </cell>
-          <cell r="I1" t="str">
-            <v>Email</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="A2" t="str">
-            <v>E009</v>
-          </cell>
-          <cell r="B2" t="str">
-            <v>East</v>
-          </cell>
-          <cell r="C2" t="str">
-            <v>Lisa Taylor</v>
-          </cell>
-          <cell r="D2" t="str">
-            <v>HR</v>
-          </cell>
-          <cell r="E2">
-            <v>46000</v>
-          </cell>
-          <cell r="F2">
-            <v>2000</v>
-          </cell>
-          <cell r="G2">
-            <v>2</v>
-          </cell>
-          <cell r="H2">
-            <v>44668</v>
-          </cell>
-          <cell r="I2" t="str">
-            <v>lisa.t@email.com</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>E015</v>
-          </cell>
-          <cell r="B3" t="str">
-            <v>West</v>
-          </cell>
-          <cell r="C3" t="str">
-            <v>Daniel Clark</v>
-          </cell>
-          <cell r="D3" t="str">
-            <v>HR</v>
-          </cell>
-          <cell r="E3">
-            <v>45000</v>
-          </cell>
-          <cell r="F3">
-            <v>2200</v>
-          </cell>
-          <cell r="G3">
-            <v>2</v>
-          </cell>
-          <cell r="H3">
-            <v>44448</v>
-          </cell>
-          <cell r="I3" t="str">
-            <v>daniel.c@email.com</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4" t="str">
-            <v>E006</v>
-          </cell>
-          <cell r="B4" t="str">
-            <v>North</v>
-          </cell>
-          <cell r="C4" t="str">
-            <v>Anna Lee</v>
-          </cell>
-          <cell r="D4" t="str">
-            <v>HR</v>
-          </cell>
-          <cell r="E4">
-            <v>47000</v>
-          </cell>
-          <cell r="F4">
-            <v>2500</v>
-          </cell>
-          <cell r="G4">
-            <v>3</v>
-          </cell>
-          <cell r="H4">
-            <v>44359</v>
-          </cell>
-          <cell r="I4" t="str">
-            <v>anna.lee@email.com</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5" t="str">
-            <v>E018</v>
-          </cell>
-          <cell r="B5" t="str">
-            <v>North</v>
-          </cell>
-          <cell r="C5" t="str">
-            <v>Olivia Hall</v>
-          </cell>
-          <cell r="D5" t="str">
-            <v>HR</v>
-          </cell>
-          <cell r="E5">
-            <v>47000</v>
-          </cell>
-          <cell r="F5">
-            <v>2600</v>
-          </cell>
-          <cell r="G5">
-            <v>3</v>
-          </cell>
-          <cell r="H5">
-            <v>44620</v>
-          </cell>
-          <cell r="I5" t="str">
-            <v>olivia.h@email.com</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>E012</v>
-          </cell>
-          <cell r="B6" t="str">
-            <v>South</v>
-          </cell>
-          <cell r="C6" t="str">
-            <v>Alex Martinez</v>
-          </cell>
-          <cell r="D6" t="str">
-            <v>HR</v>
-          </cell>
-          <cell r="E6">
-            <v>49000</v>
-          </cell>
-          <cell r="F6">
-            <v>2800</v>
-          </cell>
-          <cell r="G6">
-            <v>3</v>
-          </cell>
-          <cell r="H6">
-            <v>44115</v>
-          </cell>
-          <cell r="I6" t="str">
-            <v>alex.m@email.com</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7" t="str">
-            <v>E002</v>
-          </cell>
-          <cell r="B7" t="str">
-            <v>West</v>
-          </cell>
-          <cell r="C7" t="str">
-            <v>Sara Khan</v>
-          </cell>
-          <cell r="D7" t="str">
-            <v>HR</v>
-          </cell>
-          <cell r="E7">
-            <v>48000</v>
-          </cell>
-          <cell r="F7">
-            <v>3000</v>
-          </cell>
-          <cell r="G7">
-            <v>3</v>
-          </cell>
-          <cell r="H7">
-            <v>44022</v>
-          </cell>
-          <cell r="I7" t="str">
-            <v>sara.khan@email.com</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8" t="str">
-            <v>E019</v>
-          </cell>
-          <cell r="B8" t="str">
-            <v>West</v>
-          </cell>
-          <cell r="C8" t="str">
-            <v>Ethan Allen</v>
-          </cell>
-          <cell r="D8" t="str">
-            <v>Sales</v>
-          </cell>
-          <cell r="E8">
-            <v>52000</v>
-          </cell>
-          <cell r="F8">
-            <v>3900</v>
-          </cell>
-          <cell r="G8">
-            <v>4</v>
-          </cell>
-          <cell r="H8">
-            <v>44329</v>
-          </cell>
-          <cell r="I8" t="str">
-            <v>ethan.a@email.com</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9" t="str">
-            <v>E007</v>
-          </cell>
-          <cell r="B9" t="str">
-            <v>West</v>
-          </cell>
-          <cell r="C9" t="str">
-            <v>Chris Brown</v>
-          </cell>
-          <cell r="D9" t="str">
-            <v>Sales</v>
-          </cell>
-          <cell r="E9">
-            <v>51000</v>
-          </cell>
-          <cell r="F9">
-            <v>4000</v>
-          </cell>
-          <cell r="G9">
-            <v>4</v>
-          </cell>
-          <cell r="H9">
-            <v>43886</v>
-          </cell>
-          <cell r="I9" t="str">
-            <v>chris.b@email.com</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10" t="str">
-            <v>E010</v>
-          </cell>
-          <cell r="B10" t="str">
-            <v>North</v>
-          </cell>
-          <cell r="C10" t="str">
-            <v>Tom Anderson</v>
-          </cell>
-          <cell r="D10" t="str">
-            <v>Sales</v>
-          </cell>
-          <cell r="E10">
-            <v>53000</v>
-          </cell>
-          <cell r="F10">
-            <v>4200</v>
-          </cell>
-          <cell r="G10">
-            <v>4</v>
-          </cell>
-          <cell r="H10">
-            <v>44531</v>
-          </cell>
-          <cell r="I10" t="str">
-            <v>tom.a@email.com</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11" t="str">
-            <v>E004</v>
-          </cell>
-          <cell r="B11" t="str">
-            <v>South</v>
-          </cell>
-          <cell r="C11" t="str">
-            <v>Emily Davis</v>
-          </cell>
-          <cell r="D11" t="str">
-            <v>Sales</v>
-          </cell>
-          <cell r="E11">
-            <v>54000</v>
-          </cell>
-          <cell r="F11">
-            <v>4500</v>
-          </cell>
-          <cell r="G11">
-            <v>4</v>
-          </cell>
-          <cell r="H11">
-            <v>44566</v>
-          </cell>
-          <cell r="I11" t="str">
-            <v>emily.d@email.com</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12" t="str">
-            <v>E013</v>
-          </cell>
-          <cell r="B12" t="str">
-            <v>East</v>
-          </cell>
-          <cell r="C12" t="str">
-            <v>Kevin White</v>
-          </cell>
-          <cell r="D12" t="str">
-            <v>Sales</v>
-          </cell>
-          <cell r="E12">
-            <v>55000</v>
-          </cell>
-          <cell r="F12">
-            <v>4700</v>
-          </cell>
-          <cell r="G12">
-            <v>4</v>
-          </cell>
-          <cell r="H12">
-            <v>43527</v>
-          </cell>
-          <cell r="I12" t="str">
-            <v>kevin.w@email.com</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13" t="str">
-            <v>E016</v>
-          </cell>
-          <cell r="B13" t="str">
-            <v>South</v>
-          </cell>
-          <cell r="C13" t="str">
-            <v>Sophia Lewis</v>
-          </cell>
-          <cell r="D13" t="str">
-            <v>Sales</v>
-          </cell>
-          <cell r="E13">
-            <v>56000</v>
-          </cell>
-          <cell r="F13">
-            <v>4800</v>
-          </cell>
-          <cell r="G13">
-            <v>4</v>
-          </cell>
-          <cell r="H13">
-            <v>43849</v>
-          </cell>
-          <cell r="I13" t="str">
-            <v>sophia.l@email.com</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14" t="str">
-            <v>E001</v>
-          </cell>
-          <cell r="B14" t="str">
-            <v>East</v>
-          </cell>
-          <cell r="C14" t="str">
-            <v>John Smith</v>
-          </cell>
-          <cell r="D14" t="str">
-            <v>Sales</v>
-          </cell>
-          <cell r="E14">
-            <v>52000</v>
-          </cell>
-          <cell r="F14">
-            <v>5000</v>
-          </cell>
-          <cell r="G14">
-            <v>4</v>
-          </cell>
-          <cell r="H14">
-            <v>44270</v>
-          </cell>
-          <cell r="I14" t="str">
-            <v>john.smith@email.com</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15" t="str">
-            <v>E008</v>
-          </cell>
-          <cell r="B15" t="str">
-            <v>South</v>
-          </cell>
-          <cell r="C15" t="str">
-            <v>David Wilson</v>
-          </cell>
-          <cell r="D15" t="str">
-            <v>IT</v>
-          </cell>
-          <cell r="E15">
-            <v>68000</v>
-          </cell>
-          <cell r="F15">
-            <v>6000</v>
-          </cell>
-          <cell r="G15">
-            <v>5</v>
-          </cell>
-          <cell r="H15">
-            <v>43707</v>
-          </cell>
-          <cell r="I15" t="str">
-            <v>david.w@email.com</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16" t="str">
-            <v>E003</v>
-          </cell>
-          <cell r="B16" t="str">
-            <v>North</v>
-          </cell>
-          <cell r="C16" t="str">
-            <v>Mike Johnson</v>
-          </cell>
-          <cell r="D16" t="str">
-            <v>IT</v>
-          </cell>
-          <cell r="E16">
-            <v>65000</v>
-          </cell>
-          <cell r="F16">
-            <v>7000</v>
-          </cell>
-          <cell r="G16">
-            <v>5</v>
-          </cell>
-          <cell r="H16">
-            <v>43791</v>
-          </cell>
-          <cell r="I16" t="str">
-            <v>mike.j@email.com</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17" t="str">
-            <v>E017</v>
-          </cell>
-          <cell r="B17" t="str">
-            <v>East</v>
-          </cell>
-          <cell r="C17" t="str">
-            <v>James Walker</v>
-          </cell>
-          <cell r="D17" t="str">
-            <v>IT</v>
-          </cell>
-          <cell r="E17">
-            <v>69000</v>
-          </cell>
-          <cell r="F17">
-            <v>7100</v>
-          </cell>
-          <cell r="G17">
-            <v>5</v>
-          </cell>
-          <cell r="H17">
-            <v>43622</v>
-          </cell>
-          <cell r="I17" t="str">
-            <v>james.w@email.com</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="A18" t="str">
-            <v>E011</v>
-          </cell>
-          <cell r="B18" t="str">
-            <v>West</v>
-          </cell>
-          <cell r="C18" t="str">
-            <v>Nina Gupta</v>
-          </cell>
-          <cell r="D18" t="str">
-            <v>IT</v>
-          </cell>
-          <cell r="E18">
-            <v>70000</v>
-          </cell>
-          <cell r="F18">
-            <v>7500</v>
-          </cell>
-          <cell r="G18">
-            <v>5</v>
-          </cell>
-          <cell r="H18">
-            <v>43241</v>
-          </cell>
-          <cell r="I18" t="str">
-            <v>nina.g@email.com</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19" t="str">
-            <v>E020</v>
-          </cell>
-          <cell r="B19" t="str">
-            <v>South</v>
-          </cell>
-          <cell r="C19" t="str">
-            <v>Chloe Young</v>
-          </cell>
-          <cell r="D19" t="str">
-            <v>IT</v>
-          </cell>
-          <cell r="E19">
-            <v>71000</v>
-          </cell>
-          <cell r="F19">
-            <v>7800</v>
-          </cell>
-          <cell r="G19">
-            <v>5</v>
-          </cell>
-          <cell r="H19">
-            <v>43458</v>
-          </cell>
-          <cell r="I19" t="str">
-            <v>chloe.y@email.com</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="A20" t="str">
-            <v>E005</v>
-          </cell>
-          <cell r="B20" t="str">
-            <v>East</v>
-          </cell>
-          <cell r="C20" t="str">
-            <v>Raj Patel</v>
-          </cell>
-          <cell r="D20" t="str">
-            <v>IT</v>
-          </cell>
-          <cell r="E20">
-            <v>72000</v>
-          </cell>
-          <cell r="F20">
-            <v>8000</v>
-          </cell>
-          <cell r="G20">
-            <v>5</v>
-          </cell>
-          <cell r="H20">
-            <v>43361</v>
-          </cell>
-          <cell r="I20" t="str">
-            <v>raj.patel@email.com</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="A21" t="str">
-            <v>E014</v>
-          </cell>
-          <cell r="B21" t="str">
-            <v>North</v>
-          </cell>
-          <cell r="C21" t="str">
-            <v>Priya Sharma</v>
-          </cell>
-          <cell r="D21" t="str">
-            <v>IT</v>
-          </cell>
-          <cell r="E21">
-            <v>73000</v>
-          </cell>
-          <cell r="F21">
-            <v>8200</v>
-          </cell>
-          <cell r="G21">
-            <v>5</v>
-          </cell>
-          <cell r="H21">
-            <v>42930</v>
-          </cell>
-          <cell r="I21" t="str">
-            <v>priya.s@email.com</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1837,7 +1260,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:C15" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="9">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -2239,1001 +1662,1251 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:X23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.77734375" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.21875" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="2"/>
+    <col min="4" max="4" width="11.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="5.88671875" style="42" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="8.88671875" style="2"/>
+    <col min="10" max="10" width="6.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A1" s="46" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="49"/>
+      <c r="J1" s="46" t="s">
+        <v>189</v>
+      </c>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="46"/>
+      <c r="Q1" s="46"/>
+      <c r="R1" s="46"/>
+    </row>
+    <row r="2" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D2" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="H1" s="6" t="s">
+      <c r="E2" s="49"/>
+      <c r="F2" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="G2" s="51" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="K2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="L2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="M2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="N2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="O2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="P2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="Q2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="R2" s="6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="U2" s="48" t="s">
+        <v>190</v>
+      </c>
+      <c r="V2" s="48"/>
+      <c r="W2" s="48"/>
+      <c r="X2" s="48"/>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A3" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="3" t="str">
-        <f>VLOOKUP(A2,[1]Sheet5!$A$1:$I$21,1,FALSE)</f>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50" t="str">
+        <f>VLOOKUP($A3,$J$2:$R$22,1,FALSE)</f>
         <v>E001</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="G3" s="50">
+        <f>VLOOKUP($A3,$J$2:$R$22,5,FALSE)</f>
+        <v>52000</v>
+      </c>
+      <c r="H3" s="50">
+        <f>VLOOKUP($A3,$J$2:$R$22,7,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="K3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="L3" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="M3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="7">
+      <c r="N3" s="7">
         <v>46000</v>
       </c>
-      <c r="M2" s="7">
+      <c r="O3" s="7">
         <v>2000</v>
       </c>
-      <c r="N2" s="7">
+      <c r="P3" s="7">
         <v>2</v>
       </c>
-      <c r="O2" s="8">
+      <c r="Q3" s="8">
         <v>44668</v>
       </c>
-      <c r="P2" s="9" t="s">
+      <c r="R3" s="9" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="W3" s="48"/>
+      <c r="X3" s="48"/>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="C4" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="3" t="str">
-        <f>VLOOKUP(A3,[1]Sheet5!$A$1:$I$21,1,FALSE)</f>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50" t="str">
+        <f t="shared" ref="F4:F23" si="0">VLOOKUP(A4,$J$2:$R$22,1,FALSE)</f>
         <v>E002</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="G4" s="50">
+        <f t="shared" ref="G4:G23" si="1">VLOOKUP($A4,$J$2:$R$22,5,FALSE)</f>
+        <v>48000</v>
+      </c>
+      <c r="H4" s="50">
+        <f t="shared" ref="H4:H23" si="2">VLOOKUP($A4,$J$2:$R$22,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="J4" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="K4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="L4" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="M4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="7">
+      <c r="N4" s="7">
         <v>45000</v>
       </c>
-      <c r="M3" s="7">
+      <c r="O4" s="7">
         <v>2200</v>
       </c>
-      <c r="N3" s="7">
+      <c r="P4" s="7">
         <v>2</v>
       </c>
-      <c r="O3" s="8">
+      <c r="Q4" s="8">
         <v>44448</v>
       </c>
-      <c r="P3" s="9" t="s">
+      <c r="R4" s="9" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="W4" s="48"/>
+      <c r="X4" s="48"/>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C5" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="3" t="str">
-        <f>VLOOKUP(A4,[1]Sheet5!$A$1:$I$21,1,FALSE)</f>
+      <c r="E5" s="50"/>
+      <c r="F5" s="50" t="str">
+        <f t="shared" si="0"/>
         <v>E003</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="G5" s="50">
+        <f t="shared" si="1"/>
+        <v>65000</v>
+      </c>
+      <c r="H5" s="50">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="J5" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="K5" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="L5" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="M5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="L4" s="7">
+      <c r="N5" s="7">
         <v>47000</v>
       </c>
-      <c r="M4" s="7">
+      <c r="O5" s="7">
         <v>2500</v>
       </c>
-      <c r="N4" s="7">
+      <c r="P5" s="7">
         <v>3</v>
       </c>
-      <c r="O4" s="8">
+      <c r="Q5" s="8">
         <v>44359</v>
       </c>
-      <c r="P4" s="9" t="s">
+      <c r="R5" s="9" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="U5" s="48"/>
+      <c r="V5" s="48"/>
+      <c r="W5" s="48"/>
+      <c r="X5" s="48"/>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="C6" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="3" t="str">
-        <f>VLOOKUP(A5,[1]Sheet5!$A$1:$I$21,1,FALSE)</f>
+      <c r="E6" s="50"/>
+      <c r="F6" s="50" t="str">
+        <f t="shared" si="0"/>
         <v>E004</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="G6" s="50">
+        <f t="shared" si="1"/>
+        <v>54000</v>
+      </c>
+      <c r="H6" s="50">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="J6" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="K6" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="L6" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="M6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="L5" s="7">
+      <c r="N6" s="7">
         <v>47000</v>
       </c>
-      <c r="M5" s="7">
+      <c r="O6" s="7">
         <v>2600</v>
       </c>
-      <c r="N5" s="7">
+      <c r="P6" s="7">
         <v>3</v>
       </c>
-      <c r="O5" s="8">
+      <c r="Q6" s="8">
         <v>44620</v>
       </c>
-      <c r="P5" s="9" t="s">
+      <c r="R6" s="9" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B7" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C7" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D7" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="3" t="str">
-        <f>VLOOKUP(A6,[1]Sheet5!$A$1:$I$21,1,FALSE)</f>
+      <c r="E7" s="50"/>
+      <c r="F7" s="50" t="str">
+        <f t="shared" si="0"/>
         <v>E005</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="G7" s="50">
+        <f t="shared" si="1"/>
+        <v>72000</v>
+      </c>
+      <c r="H7" s="50">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="J7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="K7" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="L7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="M7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="L6" s="7">
+      <c r="N7" s="7">
         <v>49000</v>
       </c>
-      <c r="M6" s="7">
+      <c r="O7" s="7">
         <v>2800</v>
       </c>
-      <c r="N6" s="7">
+      <c r="P7" s="7">
         <v>3</v>
       </c>
-      <c r="O6" s="8">
+      <c r="Q7" s="8">
         <v>44115</v>
       </c>
-      <c r="P6" s="9" t="s">
+      <c r="R7" s="9" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="3" t="s">
+      <c r="C8" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="3" t="str">
-        <f>VLOOKUP(A7,[1]Sheet5!$A$1:$I$21,1,FALSE)</f>
+      <c r="E8" s="50"/>
+      <c r="F8" s="50" t="str">
+        <f t="shared" si="0"/>
         <v>E006</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="G8" s="50">
+        <f t="shared" si="1"/>
+        <v>47000</v>
+      </c>
+      <c r="H8" s="50">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="J8" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="K8" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="L8" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="K7" s="7" t="s">
+      <c r="M8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="L7" s="7">
+      <c r="N8" s="7">
         <v>48000</v>
       </c>
-      <c r="M7" s="7">
+      <c r="O8" s="7">
         <v>3000</v>
       </c>
-      <c r="N7" s="7">
+      <c r="P8" s="7">
         <v>3</v>
       </c>
-      <c r="O7" s="8">
+      <c r="Q8" s="8">
         <v>44022</v>
       </c>
-      <c r="P7" s="9" t="s">
+      <c r="R8" s="9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C9" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D9" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="3" t="str">
-        <f>VLOOKUP(A8,[1]Sheet5!$A$1:$I$21,1,FALSE)</f>
+      <c r="E9" s="50"/>
+      <c r="F9" s="50" t="str">
+        <f t="shared" si="0"/>
         <v>E007</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="G9" s="50">
+        <f t="shared" si="1"/>
+        <v>51000</v>
+      </c>
+      <c r="H9" s="50">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="J9" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="K9" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="L9" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="K8" s="7" t="s">
+      <c r="M9" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="L8" s="7">
+      <c r="N9" s="7">
         <v>52000</v>
       </c>
-      <c r="M8" s="7">
+      <c r="O9" s="7">
         <v>3900</v>
       </c>
-      <c r="N8" s="7">
+      <c r="P9" s="7">
         <v>4</v>
       </c>
-      <c r="O8" s="8">
+      <c r="Q9" s="8">
         <v>44329</v>
       </c>
-      <c r="P8" s="9" t="s">
+      <c r="R9" s="9" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C10" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D10" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="3" t="str">
-        <f>VLOOKUP(A9,[1]Sheet5!$A$1:$I$21,1,FALSE)</f>
+      <c r="E10" s="50"/>
+      <c r="F10" s="50" t="str">
+        <f t="shared" si="0"/>
         <v>E008</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="G10" s="50">
+        <f t="shared" si="1"/>
+        <v>68000</v>
+      </c>
+      <c r="H10" s="50">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="J10" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="K10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="L10" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="K9" s="7" t="s">
+      <c r="M10" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="L9" s="7">
+      <c r="N10" s="7">
         <v>51000</v>
       </c>
-      <c r="M9" s="7">
+      <c r="O10" s="7">
         <v>4000</v>
       </c>
-      <c r="N9" s="7">
+      <c r="P10" s="7">
         <v>4</v>
       </c>
-      <c r="O9" s="8">
+      <c r="Q10" s="8">
         <v>43886</v>
       </c>
-      <c r="P9" s="9" t="s">
+      <c r="R10" s="9" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="3" t="s">
+      <c r="C11" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="3" t="str">
-        <f>VLOOKUP(A10,[1]Sheet5!$A$1:$I$21,1,FALSE)</f>
+      <c r="E11" s="50"/>
+      <c r="F11" s="50" t="str">
+        <f t="shared" si="0"/>
         <v>E009</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="G11" s="50">
+        <f t="shared" si="1"/>
+        <v>46000</v>
+      </c>
+      <c r="H11" s="50">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="J11" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="K11" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="L11" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="K10" s="7" t="s">
+      <c r="M11" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="L10" s="7">
+      <c r="N11" s="7">
         <v>53000</v>
       </c>
-      <c r="M10" s="7">
+      <c r="O11" s="7">
         <v>4200</v>
       </c>
-      <c r="N10" s="7">
+      <c r="P11" s="7">
         <v>4</v>
       </c>
-      <c r="O10" s="8">
+      <c r="Q11" s="8">
         <v>44531</v>
       </c>
-      <c r="P10" s="9" t="s">
+      <c r="R11" s="9" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C12" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D12" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="3" t="str">
-        <f>VLOOKUP(A11,[1]Sheet5!$A$1:$I$21,1,FALSE)</f>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50" t="str">
+        <f t="shared" si="0"/>
         <v>E010</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="G12" s="50">
+        <f t="shared" si="1"/>
+        <v>53000</v>
+      </c>
+      <c r="H12" s="50">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="J12" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="K12" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="L12" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="K11" s="7" t="s">
+      <c r="M12" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="L11" s="7">
+      <c r="N12" s="7">
         <v>54000</v>
       </c>
-      <c r="M11" s="7">
+      <c r="O12" s="7">
         <v>4500</v>
       </c>
-      <c r="N11" s="7">
+      <c r="P12" s="7">
         <v>4</v>
       </c>
-      <c r="O11" s="8">
+      <c r="Q12" s="8">
         <v>44566</v>
       </c>
-      <c r="P11" s="9" t="s">
+      <c r="R12" s="9" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D12" s="3" t="s">
+      <c r="C13" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="3" t="str">
-        <f>VLOOKUP(A12,[1]Sheet5!$A$1:$I$21,1,FALSE)</f>
+      <c r="E13" s="50"/>
+      <c r="F13" s="50" t="str">
+        <f t="shared" si="0"/>
         <v>E011</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="G13" s="50">
+        <f t="shared" si="1"/>
+        <v>70000</v>
+      </c>
+      <c r="H13" s="50">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="J13" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="I12" s="7" t="s">
+      <c r="K13" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="L13" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="K12" s="7" t="s">
+      <c r="M13" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="L12" s="7">
+      <c r="N13" s="7">
         <v>55000</v>
       </c>
-      <c r="M12" s="7">
+      <c r="O13" s="7">
         <v>4700</v>
       </c>
-      <c r="N12" s="7">
+      <c r="P13" s="7">
         <v>4</v>
       </c>
-      <c r="O12" s="8">
+      <c r="Q13" s="8">
         <v>43527</v>
       </c>
-      <c r="P12" s="9" t="s">
+      <c r="R13" s="9" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C14" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D14" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="3" t="str">
-        <f>VLOOKUP(A13,[1]Sheet5!$A$1:$I$21,1,FALSE)</f>
+      <c r="E14" s="50"/>
+      <c r="F14" s="50" t="str">
+        <f t="shared" si="0"/>
         <v>E012</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="G14" s="50">
+        <f t="shared" si="1"/>
+        <v>49000</v>
+      </c>
+      <c r="H14" s="50">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="J14" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="I13" s="7" t="s">
+      <c r="K14" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="J13" s="7" t="s">
+      <c r="L14" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="K13" s="7" t="s">
+      <c r="M14" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="L13" s="7">
+      <c r="N14" s="7">
         <v>56000</v>
       </c>
-      <c r="M13" s="7">
+      <c r="O14" s="7">
         <v>4800</v>
       </c>
-      <c r="N13" s="7">
+      <c r="P14" s="7">
         <v>4</v>
       </c>
-      <c r="O13" s="8">
+      <c r="Q14" s="8">
         <v>43849</v>
       </c>
-      <c r="P13" s="9" t="s">
+      <c r="R14" s="9" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B15" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C15" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="3" t="str">
-        <f>VLOOKUP(A14,[1]Sheet5!$A$1:$I$21,1,FALSE)</f>
+      <c r="E15" s="50"/>
+      <c r="F15" s="50" t="str">
+        <f t="shared" si="0"/>
         <v>E013</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="G15" s="50">
+        <f t="shared" si="1"/>
+        <v>55000</v>
+      </c>
+      <c r="H15" s="50">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="J15" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I14" s="7" t="s">
+      <c r="K15" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="J14" s="7" t="s">
+      <c r="L15" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="K14" s="7" t="s">
+      <c r="M15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="L14" s="7">
+      <c r="N15" s="7">
         <v>52000</v>
       </c>
-      <c r="M14" s="7">
+      <c r="O15" s="7">
         <v>5000</v>
       </c>
-      <c r="N14" s="7">
+      <c r="P15" s="7">
         <v>4</v>
       </c>
-      <c r="O14" s="8">
+      <c r="Q15" s="8">
         <v>44270</v>
       </c>
-      <c r="P14" s="9" t="s">
+      <c r="R15" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B16" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D15" s="3" t="s">
+      <c r="C16" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="3" t="str">
-        <f>VLOOKUP(A15,[1]Sheet5!$A$1:$I$21,1,FALSE)</f>
+      <c r="E16" s="50"/>
+      <c r="F16" s="50" t="str">
+        <f t="shared" si="0"/>
         <v>E014</v>
       </c>
-      <c r="H15" s="7" t="s">
+      <c r="G16" s="50">
+        <f t="shared" si="1"/>
+        <v>73000</v>
+      </c>
+      <c r="H16" s="50">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="J16" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="I15" s="7" t="s">
+      <c r="K16" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="J15" s="7" t="s">
+      <c r="L16" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="K15" s="7" t="s">
+      <c r="M16" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="L15" s="7">
+      <c r="N16" s="7">
         <v>68000</v>
       </c>
-      <c r="M15" s="7">
+      <c r="O16" s="7">
         <v>6000</v>
       </c>
-      <c r="N15" s="7">
+      <c r="P16" s="7">
         <v>5</v>
       </c>
-      <c r="O15" s="8">
+      <c r="Q16" s="8">
         <v>43707</v>
       </c>
-      <c r="P15" s="9" t="s">
+      <c r="R16" s="9" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A17" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B17" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C17" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D17" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E16" s="3" t="str">
-        <f>VLOOKUP(A16,[1]Sheet5!$A$1:$I$21,1,FALSE)</f>
+      <c r="E17" s="50"/>
+      <c r="F17" s="50" t="str">
+        <f t="shared" si="0"/>
         <v>E015</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="G17" s="50">
+        <f t="shared" si="1"/>
+        <v>45000</v>
+      </c>
+      <c r="H17" s="50">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="J17" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="I16" s="7" t="s">
+      <c r="K17" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="J16" s="7" t="s">
+      <c r="L17" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K16" s="7" t="s">
+      <c r="M17" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="L16" s="7">
+      <c r="N17" s="7">
         <v>65000</v>
       </c>
-      <c r="M16" s="7">
+      <c r="O17" s="7">
         <v>7000</v>
       </c>
-      <c r="N16" s="7">
+      <c r="P17" s="7">
         <v>5</v>
       </c>
-      <c r="O16" s="8">
+      <c r="Q17" s="8">
         <v>43791</v>
       </c>
-      <c r="P16" s="9" t="s">
+      <c r="R17" s="9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D17" s="3" t="s">
+      <c r="C18" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="3" t="str">
-        <f>VLOOKUP(A17,[1]Sheet5!$A$1:$I$21,1,FALSE)</f>
+      <c r="E18" s="50"/>
+      <c r="F18" s="50" t="str">
+        <f t="shared" si="0"/>
         <v>E016</v>
       </c>
-      <c r="H17" s="7" t="s">
+      <c r="G18" s="50">
+        <f t="shared" si="1"/>
+        <v>56000</v>
+      </c>
+      <c r="H18" s="50">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="J18" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I17" s="7" t="s">
+      <c r="K18" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="J17" s="7" t="s">
+      <c r="L18" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="K17" s="7" t="s">
+      <c r="M18" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="L17" s="7">
+      <c r="N18" s="7">
         <v>69000</v>
       </c>
-      <c r="M17" s="7">
+      <c r="O18" s="7">
         <v>7100</v>
       </c>
-      <c r="N17" s="7">
+      <c r="P18" s="7">
         <v>5</v>
       </c>
-      <c r="O17" s="8">
+      <c r="Q18" s="8">
         <v>43622</v>
       </c>
-      <c r="P17" s="9" t="s">
+      <c r="R18" s="9" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C19" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D19" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="3" t="str">
-        <f>VLOOKUP(A18,[1]Sheet5!$A$1:$I$21,1,FALSE)</f>
+      <c r="E19" s="50"/>
+      <c r="F19" s="50" t="str">
+        <f t="shared" si="0"/>
         <v>E017</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="G19" s="50">
+        <f t="shared" si="1"/>
+        <v>69000</v>
+      </c>
+      <c r="H19" s="50">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="J19" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="I18" s="7" t="s">
+      <c r="K19" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="J18" s="7" t="s">
+      <c r="L19" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="K18" s="7" t="s">
+      <c r="M19" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="L18" s="7">
+      <c r="N19" s="7">
         <v>70000</v>
       </c>
-      <c r="M18" s="7">
+      <c r="O19" s="7">
         <v>7500</v>
       </c>
-      <c r="N18" s="7">
+      <c r="P19" s="7">
         <v>5</v>
       </c>
-      <c r="O18" s="8">
+      <c r="Q19" s="8">
         <v>43241</v>
       </c>
-      <c r="P18" s="9" t="s">
+      <c r="R19" s="9" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B20" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D19" s="3" t="s">
+      <c r="C20" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D20" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E19" s="3" t="str">
-        <f>VLOOKUP(A19,[1]Sheet5!$A$1:$I$21,1,FALSE)</f>
+      <c r="E20" s="50"/>
+      <c r="F20" s="50" t="str">
+        <f t="shared" si="0"/>
         <v>E018</v>
       </c>
-      <c r="H19" s="7" t="s">
+      <c r="G20" s="50">
+        <f t="shared" si="1"/>
+        <v>47000</v>
+      </c>
+      <c r="H20" s="50">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="J20" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="I19" s="7" t="s">
+      <c r="K20" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="J19" s="7" t="s">
+      <c r="L20" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="K19" s="7" t="s">
+      <c r="M20" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="L19" s="7">
+      <c r="N20" s="7">
         <v>71000</v>
       </c>
-      <c r="M19" s="7">
+      <c r="O20" s="7">
         <v>7800</v>
       </c>
-      <c r="N19" s="7">
+      <c r="P20" s="7">
         <v>5</v>
       </c>
-      <c r="O19" s="8">
+      <c r="Q20" s="8">
         <v>43458</v>
       </c>
-      <c r="P19" s="9" t="s">
+      <c r="R20" s="9" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A21" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B21" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C21" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D21" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E20" s="3" t="str">
-        <f>VLOOKUP(A20,[1]Sheet5!$A$1:$I$21,1,FALSE)</f>
+      <c r="E21" s="50"/>
+      <c r="F21" s="50" t="str">
+        <f t="shared" si="0"/>
         <v>E019</v>
       </c>
-      <c r="H20" s="7" t="s">
+      <c r="G21" s="50">
+        <f t="shared" si="1"/>
+        <v>52000</v>
+      </c>
+      <c r="H21" s="50">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="J21" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="I20" s="7" t="s">
+      <c r="K21" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="J20" s="7" t="s">
+      <c r="L21" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="K20" s="7" t="s">
+      <c r="M21" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="L20" s="7">
+      <c r="N21" s="7">
         <v>72000</v>
       </c>
-      <c r="M20" s="7">
+      <c r="O21" s="7">
         <v>8000</v>
       </c>
-      <c r="N20" s="7">
+      <c r="P21" s="7">
         <v>5</v>
       </c>
-      <c r="O20" s="8">
+      <c r="Q21" s="8">
         <v>43361</v>
       </c>
-      <c r="P20" s="9" t="s">
+      <c r="R21" s="9" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B22" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D21" s="3" t="s">
+      <c r="C22" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E21" s="3" t="str">
-        <f>VLOOKUP(A21,[1]Sheet5!$A$1:$I$21,1,FALSE)</f>
+      <c r="E22" s="50"/>
+      <c r="F22" s="50" t="str">
+        <f t="shared" si="0"/>
         <v>E020</v>
       </c>
-      <c r="H21" s="7" t="s">
+      <c r="G22" s="50">
+        <f t="shared" si="1"/>
+        <v>71000</v>
+      </c>
+      <c r="H22" s="50">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="J22" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="I21" s="7" t="s">
+      <c r="K22" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="J21" s="7" t="s">
+      <c r="L22" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="K21" s="7" t="s">
+      <c r="M22" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="L21" s="7">
+      <c r="N22" s="7">
         <v>73000</v>
       </c>
-      <c r="M21" s="7">
+      <c r="O22" s="7">
         <v>8200</v>
       </c>
-      <c r="N21" s="7">
+      <c r="P22" s="7">
         <v>5</v>
       </c>
-      <c r="O21" s="8">
+      <c r="Q22" s="8">
         <v>42930</v>
       </c>
-      <c r="P21" s="9" t="s">
+      <c r="R22" s="9" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A23" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B23" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C23" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D23" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E22" s="3" t="e">
-        <f>VLOOKUP(A22,[1]Sheet5!$A$1:$I$21,1,FALSE)</f>
+      <c r="E23" s="50"/>
+      <c r="F23" s="50" t="e">
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
+      <c r="G23" s="50" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="H23" s="50" t="e">
+        <f t="shared" si="2"/>
+        <v>#N/A</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="J1:R1"/>
+    <mergeCell ref="U2:X5"/>
+  </mergeCells>
   <hyperlinks>
-    <hyperlink ref="P19" r:id="rId1" display="mailto:chloe.y@email.com"/>
-    <hyperlink ref="P8" r:id="rId2" display="mailto:ethan.a@email.com"/>
-    <hyperlink ref="P5" r:id="rId3" display="mailto:olivia.h@email.com"/>
-    <hyperlink ref="P17" r:id="rId4" display="mailto:james.w@email.com"/>
-    <hyperlink ref="P13" r:id="rId5" display="mailto:sophia.l@email.com"/>
-    <hyperlink ref="P3" r:id="rId6" display="mailto:daniel.c@email.com"/>
-    <hyperlink ref="P21" r:id="rId7" display="mailto:priya.s@email.com"/>
-    <hyperlink ref="P12" r:id="rId8" display="mailto:kevin.w@email.com"/>
-    <hyperlink ref="P6" r:id="rId9" display="mailto:alex.m@email.com"/>
-    <hyperlink ref="P18" r:id="rId10" display="mailto:nina.g@email.com"/>
-    <hyperlink ref="P10" r:id="rId11" display="mailto:tom.a@email.com"/>
-    <hyperlink ref="P2" r:id="rId12" display="mailto:lisa.t@email.com"/>
-    <hyperlink ref="P15" r:id="rId13" display="mailto:david.w@email.com"/>
-    <hyperlink ref="P9" r:id="rId14" display="mailto:chris.b@email.com"/>
-    <hyperlink ref="P4" r:id="rId15" display="mailto:anna.lee@email.com"/>
-    <hyperlink ref="P20" r:id="rId16" display="mailto:raj.patel@email.com"/>
-    <hyperlink ref="P11" r:id="rId17" display="mailto:emily.d@email.com"/>
-    <hyperlink ref="P16" r:id="rId18" display="mailto:mike.j@email.com"/>
-    <hyperlink ref="P7" r:id="rId19" display="mailto:sara.khan@email.com"/>
-    <hyperlink ref="P14" r:id="rId20" display="mailto:john.smith@email.com"/>
+    <hyperlink ref="R20" r:id="rId1" display="mailto:chloe.y@email.com"/>
+    <hyperlink ref="R9" r:id="rId2" display="mailto:ethan.a@email.com"/>
+    <hyperlink ref="R6" r:id="rId3" display="mailto:olivia.h@email.com"/>
+    <hyperlink ref="R18" r:id="rId4" display="mailto:james.w@email.com"/>
+    <hyperlink ref="R14" r:id="rId5" display="mailto:sophia.l@email.com"/>
+    <hyperlink ref="R4" r:id="rId6" display="mailto:daniel.c@email.com"/>
+    <hyperlink ref="R22" r:id="rId7" display="mailto:priya.s@email.com"/>
+    <hyperlink ref="R13" r:id="rId8" display="mailto:kevin.w@email.com"/>
+    <hyperlink ref="R7" r:id="rId9" display="mailto:alex.m@email.com"/>
+    <hyperlink ref="R19" r:id="rId10" display="mailto:nina.g@email.com"/>
+    <hyperlink ref="R11" r:id="rId11" display="mailto:tom.a@email.com"/>
+    <hyperlink ref="R3" r:id="rId12" display="mailto:lisa.t@email.com"/>
+    <hyperlink ref="R16" r:id="rId13" display="mailto:david.w@email.com"/>
+    <hyperlink ref="R10" r:id="rId14" display="mailto:chris.b@email.com"/>
+    <hyperlink ref="R5" r:id="rId15" display="mailto:anna.lee@email.com"/>
+    <hyperlink ref="R21" r:id="rId16" display="mailto:raj.patel@email.com"/>
+    <hyperlink ref="R12" r:id="rId17" display="mailto:emily.d@email.com"/>
+    <hyperlink ref="R17" r:id="rId18" display="mailto:mike.j@email.com"/>
+    <hyperlink ref="R8" r:id="rId19" display="mailto:sara.khan@email.com"/>
+    <hyperlink ref="R15" r:id="rId20" display="mailto:john.smith@email.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3543,7 +3216,7 @@
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B5" s="2" t="str">
         <f>HLOOKUP(B1,$B$12:$U$20,9,FALSE)</f>
@@ -4217,7 +3890,7 @@
     </row>
     <row r="23" spans="1:21" ht="31.2" x14ac:dyDescent="0.6">
       <c r="F23" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -4285,13 +3958,13 @@
       </c>
       <c r="L1" s="44"/>
       <c r="U1" s="13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="V1" s="13"/>
       <c r="W1" s="13"/>
       <c r="X1" s="13"/>
       <c r="Y1" s="45" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Z1" s="45"/>
     </row>
@@ -4300,13 +3973,13 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D2" s="11" t="s">
         <v>141</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>142</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>4</v>
@@ -4330,10 +4003,10 @@
         <v>10</v>
       </c>
       <c r="L2" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>143</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>93</v>
@@ -4348,29 +4021,29 @@
         <v>92</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="S2" s="12"/>
       <c r="T2" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="U2" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="V2" s="43" t="s">
+        <v>182</v>
+      </c>
+      <c r="W2" s="43" t="s">
+        <v>183</v>
+      </c>
+      <c r="X2" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y2" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="U2" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="V2" s="43" t="s">
-        <v>183</v>
-      </c>
-      <c r="W2" s="43" t="s">
-        <v>184</v>
-      </c>
-      <c r="X2" s="43" t="s">
-        <v>182</v>
-      </c>
-      <c r="Y2" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="Z2" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.3">
@@ -4378,10 +4051,10 @@
         <v>42</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>43</v>
@@ -4461,10 +4134,10 @@
         <v>60</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>104</v>
       </c>
       <c r="D4" s="14" t="s">
         <v>61</v>
@@ -4536,10 +4209,10 @@
         <v>33</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>106</v>
       </c>
       <c r="D5" s="14" t="s">
         <v>34</v>
@@ -4611,10 +4284,10 @@
         <v>69</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>108</v>
       </c>
       <c r="D6" s="14" t="s">
         <v>70</v>
@@ -4686,10 +4359,10 @@
         <v>51</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>110</v>
       </c>
       <c r="D7" s="14" t="s">
         <v>52</v>
@@ -4761,10 +4434,10 @@
         <v>16</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="D8" s="14" t="s">
         <v>17</v>
@@ -4836,10 +4509,10 @@
         <v>72</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="D9" s="14" t="s">
         <v>73</v>
@@ -4911,10 +4584,10 @@
         <v>36</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="D10" s="14" t="s">
         <v>37</v>
@@ -4986,10 +4659,10 @@
         <v>45</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="D11" s="14" t="s">
         <v>46</v>
@@ -5061,10 +4734,10 @@
         <v>26</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="D12" s="14" t="s">
         <v>27</v>
@@ -5136,10 +4809,10 @@
         <v>54</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>122</v>
       </c>
       <c r="D13" s="14" t="s">
         <v>55</v>
@@ -5211,10 +4884,10 @@
         <v>63</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>124</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>64</v>
@@ -5286,10 +4959,10 @@
         <v>11</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>126</v>
       </c>
       <c r="D15" s="14" t="s">
         <v>12</v>
@@ -5361,10 +5034,10 @@
         <v>39</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="D16" s="14" t="s">
         <v>40</v>
@@ -5436,10 +5109,10 @@
         <v>21</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>130</v>
       </c>
       <c r="D17" s="14" t="s">
         <v>22</v>
@@ -5511,10 +5184,10 @@
         <v>66</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>132</v>
       </c>
       <c r="D18" s="14" t="s">
         <v>67</v>
@@ -5586,10 +5259,10 @@
         <v>48</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>134</v>
       </c>
       <c r="D19" s="14" t="s">
         <v>49</v>
@@ -5661,10 +5334,10 @@
         <v>75</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>136</v>
       </c>
       <c r="D20" s="14" t="s">
         <v>76</v>
@@ -5736,10 +5409,10 @@
         <v>30</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>138</v>
       </c>
       <c r="D21" s="14" t="s">
         <v>31</v>
@@ -5811,10 +5484,10 @@
         <v>57</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>140</v>
       </c>
       <c r="D22" s="14" t="s">
         <v>58</v>
@@ -7142,7 +6815,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -7287,15 +6960,15 @@
   <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="36.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B1" s="18" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>150</v>
+        <v>186</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -7352,18 +7025,18 @@
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" s="15"/>
     </row>
-    <row r="8" spans="1:10" ht="43.2" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:10" ht="32.4" x14ac:dyDescent="0.6">
       <c r="A8" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="B8" s="18" t="s">
-        <v>157</v>
-      </c>
       <c r="C8" s="26" t="s">
-        <v>153</v>
+        <v>184</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="J8" s="28"/>
     </row>
@@ -7528,13 +7201,13 @@
   <sheetData>
     <row r="1" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B1" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="C1" s="20" t="s">
         <v>150</v>
-      </c>
-      <c r="C1" s="20" t="s">
-        <v>151</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>2</v>
@@ -7793,16 +7466,16 @@
     </row>
     <row r="8" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="B8" s="18" t="s">
-        <v>157</v>
-      </c>
       <c r="C8" s="26" t="s">
+        <v>152</v>
+      </c>
+      <c r="D8" s="20" t="s">
         <v>153</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>154</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>72</v>
@@ -8478,7 +8151,7 @@
       <c r="I1" s="37"/>
       <c r="J1" s="37"/>
       <c r="K1" s="37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L1" s="37"/>
       <c r="M1" s="37"/>
@@ -8486,15 +8159,15 @@
       <c r="O1" s="39"/>
       <c r="P1" s="39"/>
       <c r="Q1" s="39" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="R1" s="39"/>
       <c r="S1" s="39"/>
       <c r="T1" s="39" t="s">
+        <v>179</v>
+      </c>
+      <c r="U1" s="39" t="s">
         <v>180</v>
-      </c>
-      <c r="U1" s="39" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
@@ -8502,10 +8175,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="35" t="s">
+        <v>166</v>
+      </c>
+      <c r="C2" s="35" t="s">
         <v>167</v>
-      </c>
-      <c r="C2" s="35" t="s">
-        <v>168</v>
       </c>
       <c r="D2" s="35" t="s">
         <v>4</v>
@@ -8545,10 +8218,10 @@
       </c>
       <c r="P2" s="35"/>
       <c r="Q2" s="35" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R2" s="35" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="S2" s="35" t="s">
         <v>89</v>
@@ -8572,16 +8245,16 @@
       <c r="I3" s="35"/>
       <c r="J3" s="35"/>
       <c r="K3" s="35" t="s">
+        <v>157</v>
+      </c>
+      <c r="L3" s="35" t="s">
         <v>158</v>
       </c>
-      <c r="L3" s="35" t="s">
+      <c r="M3" s="35" t="s">
         <v>159</v>
       </c>
-      <c r="M3" s="35" t="s">
-        <v>160</v>
-      </c>
       <c r="N3" s="35" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O3" s="35"/>
       <c r="P3" s="35"/>
@@ -8599,7 +8272,7 @@
         <v>61</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D4" s="31" t="s">
         <v>18</v>
@@ -8826,7 +8499,7 @@
         <v>70</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D7" s="31" t="s">
         <v>18</v>
@@ -9049,7 +8722,7 @@
         <v>37</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D10" s="31" t="s">
         <v>13</v>
@@ -9487,7 +9160,7 @@
         <v>64</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D16" s="31" t="s">
         <v>13</v>
@@ -10075,42 +9748,42 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.3">
       <c r="J25" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="K25" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.3">
       <c r="J26" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="K26" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.3">
       <c r="J27" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="K27" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.3">
       <c r="J28" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.3">
       <c r="J29" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K29" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>179</v>
       </c>
     </row>
   </sheetData>
